--- a/mapping/templates/GUIDE_Doppio/API_PDS001MI_Product.xlsx
+++ b/mapping/templates/GUIDE_Doppio/API_PDS001MI_Product.xlsx
@@ -161,40 +161,6 @@
     <author>System</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Company
-The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.
-</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Facility
-The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).
-</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Product
-The field indicates the product number.
-For a product structure with a product structure class type of 00-'Standard' (i.e. discrete items), the product number is the same as the item number manufactured (the output from the manufacturing order) and is always used together with structures to describe what a product consists of and how it is manufactured.
-There are scenarios where each process is created as a product number on (PDS001) to serve as a placeholder for product structure class types other than 00-'Standard'. In the cases where the product structure class type is Formula product structure, Routing product structure, Bulk item product structure, Packaging material product structure, or Packaged item product structure, the Product number field is used to identify a process required for the manufacture of the ultimate product number.
-</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Product structure type
-The field indicates a product structure type. You can define more than one product structure per product and facility.
-</t>
-      </text>
-    </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>Parent item status
@@ -203,82 +169,6 @@
 15: Preliminary product. Approved for explosion to generate demand on lower product levels. Should primarily be used for MRP planned items. No manufacturing orders can be entered.
 20: Definite product. Normal handling, meaning manufacturing orders may be entered.
 90: The product is blocked/out of stock. No manufacturing orders can be entered and no calculation can be made.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Responsible
-The field indicates a unique user ID.
-The ID can be used for selection and sorting.
-</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Dynamic configurator
-The field indicates how product configuration should be performed.
-0: The product's configuration is not dynamic
-1: The configuration is multi-level dynamic
-2: The configuration is one-level dynamic.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>Batch recalculation
-The field indicates whether to recalculate quantities used in connection with a change of batch sizes.
-0: No.
-1: Yes - all components and operations are included are recalculated.
-2: Yes - only yield components are recalculated.</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Number of put-away cards
-The field indicates how many put-away cards that should be printed for each product and order.
-</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Number of material requisitions
-The field indicates how many material requisitions that are normally printed for each material in connection with an order.
-</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Number of labor tickets
-The field indicates the number of labor tickets that should be printed for each operation included in a product.
-This quantity is multiplied by the labor ticket multiplier for each operation, so each user may determine the number of labor tickets for an operation.
-</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Number of shop travelers
-The field indicates how many shop traveler cards should normally be printed for each order.
-</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Number of routing cards
-The field indicates how many routing cards per operation that are normally printed.
-</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Number of picking lists
-The field indicates how many picking lists that are normally printed for each order.
-</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Number of design documents
-The field indicates the number of design documents which normally should be printed for each item and order.
-</t>
       </text>
     </comment>
   </commentList>
